--- a/research/FSF.NZ/Reports/FSF.NZ_DCF_Model.xlsx
+++ b/research/FSF.NZ/Reports/FSF.NZ_DCF_Model.xlsx
@@ -923,9 +923,10 @@
       </c>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18">
-        <f> Cost of Equity (computed)</f>
-        <v>0</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>= Cost of Equity (computed)</t>
+        </is>
       </c>
       <c r="B18" s="6">
         <f>B14+B15+B16+B17</f>
